--- a/output/prediksi/evaluasi_metode.xlsx
+++ b/output/prediksi/evaluasi_metode.xlsx
@@ -472,22 +472,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D2">
         <v>210</v>
       </c>
       <c r="E2">
-        <v>1.068</v>
+        <v>1.251</v>
       </c>
       <c r="F2">
-        <v>1.674</v>
+        <v>1.929</v>
       </c>
       <c r="G2">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
       <c r="H2">
-        <v>17.082</v>
+        <v>19.402</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -498,22 +498,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D3">
         <v>210</v>
       </c>
       <c r="E3">
-        <v>1.694</v>
+        <v>1.706</v>
       </c>
       <c r="F3">
-        <v>2.695</v>
+        <v>2.709</v>
       </c>
       <c r="G3">
-        <v>1.205</v>
+        <v>1.218</v>
       </c>
       <c r="H3">
-        <v>25.247</v>
+        <v>25.356</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -524,22 +524,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D4">
         <v>210</v>
       </c>
       <c r="E4">
-        <v>2.256</v>
+        <v>2.285</v>
       </c>
       <c r="F4">
-        <v>3.811</v>
+        <v>3.838</v>
       </c>
       <c r="G4">
-        <v>1.177</v>
+        <v>1.214</v>
       </c>
       <c r="H4">
-        <v>33.221</v>
+        <v>33.603</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -550,22 +550,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D5">
         <v>210</v>
       </c>
       <c r="E5">
-        <v>2.372</v>
+        <v>2.374</v>
       </c>
       <c r="F5">
-        <v>3.658</v>
+        <v>3.659</v>
       </c>
       <c r="G5">
-        <v>-1.491</v>
+        <v>-1.486</v>
       </c>
       <c r="H5">
-        <v>36.517</v>
+        <v>36.51</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -576,22 +576,22 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D6">
         <v>210</v>
       </c>
       <c r="E6">
-        <v>2.54</v>
+        <v>2.544</v>
       </c>
       <c r="F6">
-        <v>3.868</v>
+        <v>3.872</v>
       </c>
       <c r="G6">
-        <v>-1.737</v>
+        <v>-1.731</v>
       </c>
       <c r="H6">
-        <v>38.926</v>
+        <v>38.937</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -602,22 +602,22 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D7">
         <v>210</v>
       </c>
       <c r="E7">
-        <v>0.882</v>
+        <v>0.9</v>
       </c>
       <c r="F7">
-        <v>1.522</v>
+        <v>1.519</v>
       </c>
       <c r="G7">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H7">
-        <v>14.729</v>
+        <v>14.915</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -628,22 +628,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D8">
         <v>210</v>
       </c>
       <c r="E8">
-        <v>1.118</v>
+        <v>1.104</v>
       </c>
       <c r="F8">
-        <v>2.004</v>
+        <v>1.987</v>
       </c>
       <c r="G8">
-        <v>0.583</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H8">
-        <v>19.201</v>
+        <v>18.933</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -654,22 +654,22 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D9">
         <v>210</v>
       </c>
       <c r="E9">
-        <v>1.185</v>
+        <v>1.174</v>
       </c>
       <c r="F9">
-        <v>2.184</v>
+        <v>2.171</v>
       </c>
       <c r="G9">
-        <v>0.665</v>
+        <v>0.647</v>
       </c>
       <c r="H9">
-        <v>19.268</v>
+        <v>19.052</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -680,22 +680,22 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D10">
         <v>210</v>
       </c>
       <c r="E10">
-        <v>3.166</v>
+        <v>3.152</v>
       </c>
       <c r="F10">
-        <v>5.362</v>
+        <v>5.317</v>
       </c>
       <c r="G10">
-        <v>2.358</v>
+        <v>2.332</v>
       </c>
       <c r="H10">
-        <v>46.865</v>
+        <v>46.939</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -706,22 +706,22 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>2575</v>
+        <v>2540</v>
       </c>
       <c r="D11">
         <v>210</v>
       </c>
       <c r="E11">
-        <v>3.396</v>
+        <v>3.416</v>
       </c>
       <c r="F11">
-        <v>4.923</v>
+        <v>4.944</v>
       </c>
       <c r="G11">
-        <v>-2.806</v>
+        <v>-2.82</v>
       </c>
       <c r="H11">
-        <v>48.754</v>
+        <v>48.957</v>
       </c>
     </row>
   </sheetData>

--- a/output/prediksi/evaluasi_metode.xlsx
+++ b/output/prediksi/evaluasi_metode.xlsx
@@ -487,7 +487,7 @@
         <v>0.22</v>
       </c>
       <c r="H2">
-        <v>19.402</v>
+        <v>19.403</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -617,7 +617,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H7">
-        <v>14.915</v>
+        <v>14.914</v>
       </c>
     </row>
     <row r="8" spans="1:8">

--- a/output/prediksi/evaluasi_metode.xlsx
+++ b/output/prediksi/evaluasi_metode.xlsx
@@ -478,16 +478,16 @@
         <v>210</v>
       </c>
       <c r="E2">
-        <v>1.251</v>
+        <v>1.131</v>
       </c>
       <c r="F2">
-        <v>1.929</v>
+        <v>1.826</v>
       </c>
       <c r="G2">
-        <v>0.22</v>
+        <v>0.298</v>
       </c>
       <c r="H2">
-        <v>19.403</v>
+        <v>16.948</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -513,7 +513,7 @@
         <v>1.218</v>
       </c>
       <c r="H3">
-        <v>25.356</v>
+        <v>24.125</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -539,7 +539,7 @@
         <v>1.214</v>
       </c>
       <c r="H4">
-        <v>33.603</v>
+        <v>31.977</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -565,7 +565,7 @@
         <v>-1.486</v>
       </c>
       <c r="H5">
-        <v>36.51</v>
+        <v>35.07</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -591,7 +591,7 @@
         <v>-1.731</v>
       </c>
       <c r="H6">
-        <v>38.937</v>
+        <v>37.407</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -608,16 +608,16 @@
         <v>210</v>
       </c>
       <c r="E7">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="F7">
-        <v>1.519</v>
+        <v>1.537</v>
       </c>
       <c r="G7">
-        <v>0.07000000000000001</v>
+        <v>0.177</v>
       </c>
       <c r="H7">
-        <v>14.914</v>
+        <v>13.304</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -634,16 +634,16 @@
         <v>210</v>
       </c>
       <c r="E8">
-        <v>1.104</v>
+        <v>1.105</v>
       </c>
       <c r="F8">
-        <v>1.987</v>
+        <v>1.988</v>
       </c>
       <c r="G8">
-        <v>0.5620000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H8">
-        <v>18.933</v>
+        <v>17.653</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -663,13 +663,13 @@
         <v>1.174</v>
       </c>
       <c r="F9">
-        <v>2.171</v>
+        <v>2.172</v>
       </c>
       <c r="G9">
-        <v>0.647</v>
+        <v>0.648</v>
       </c>
       <c r="H9">
-        <v>19.052</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -689,13 +689,13 @@
         <v>3.152</v>
       </c>
       <c r="F10">
-        <v>5.317</v>
+        <v>5.318</v>
       </c>
       <c r="G10">
         <v>2.332</v>
       </c>
       <c r="H10">
-        <v>46.939</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -718,10 +718,10 @@
         <v>4.944</v>
       </c>
       <c r="G11">
-        <v>-2.82</v>
+        <v>-2.819</v>
       </c>
       <c r="H11">
-        <v>48.957</v>
+        <v>46.916</v>
       </c>
     </row>
   </sheetData>

--- a/output/prediksi/evaluasi_metode.xlsx
+++ b/output/prediksi/evaluasi_metode.xlsx
@@ -472,22 +472,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E2">
-        <v>1.131</v>
+        <v>1.198</v>
       </c>
       <c r="F2">
-        <v>1.826</v>
+        <v>1.891</v>
       </c>
       <c r="G2">
-        <v>0.298</v>
+        <v>0.365</v>
       </c>
       <c r="H2">
-        <v>16.948</v>
+        <v>16.771</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -498,22 +498,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D3">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E3">
-        <v>1.706</v>
+        <v>1.696</v>
       </c>
       <c r="F3">
-        <v>2.709</v>
+        <v>2.701</v>
       </c>
       <c r="G3">
-        <v>1.218</v>
+        <v>1.211</v>
       </c>
       <c r="H3">
-        <v>24.125</v>
+        <v>22.652</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -524,22 +524,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D4">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E4">
-        <v>2.285</v>
+        <v>2.271</v>
       </c>
       <c r="F4">
-        <v>3.838</v>
+        <v>3.827</v>
       </c>
       <c r="G4">
-        <v>1.214</v>
+        <v>1.207</v>
       </c>
       <c r="H4">
-        <v>31.977</v>
+        <v>29.949</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -550,22 +550,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D5">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E5">
-        <v>2.374</v>
+        <v>2.36</v>
       </c>
       <c r="F5">
-        <v>3.659</v>
+        <v>3.648</v>
       </c>
       <c r="G5">
-        <v>-1.486</v>
+        <v>-1.477</v>
       </c>
       <c r="H5">
-        <v>35.07</v>
+        <v>33.093</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -576,22 +576,22 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D6">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E6">
-        <v>2.544</v>
+        <v>2.53</v>
       </c>
       <c r="F6">
-        <v>3.872</v>
+        <v>3.86</v>
       </c>
       <c r="G6">
-        <v>-1.731</v>
+        <v>-1.721</v>
       </c>
       <c r="H6">
-        <v>37.407</v>
+        <v>35.323</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -602,22 +602,22 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E7">
-        <v>0.86</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F7">
         <v>1.537</v>
       </c>
       <c r="G7">
-        <v>0.177</v>
+        <v>-0.11</v>
       </c>
       <c r="H7">
-        <v>13.304</v>
+        <v>13.712</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -628,22 +628,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E8">
-        <v>1.105</v>
+        <v>1.099</v>
       </c>
       <c r="F8">
-        <v>1.988</v>
+        <v>1.982</v>
       </c>
       <c r="G8">
-        <v>0.5629999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H8">
-        <v>17.653</v>
+        <v>16.354</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -654,22 +654,22 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D9">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E9">
-        <v>1.174</v>
+        <v>1.168</v>
       </c>
       <c r="F9">
-        <v>2.172</v>
+        <v>2.166</v>
       </c>
       <c r="G9">
-        <v>0.648</v>
+        <v>0.645</v>
       </c>
       <c r="H9">
-        <v>17.81</v>
+        <v>16.719</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -680,22 +680,22 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D10">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E10">
-        <v>3.152</v>
+        <v>3.134</v>
       </c>
       <c r="F10">
-        <v>5.318</v>
+        <v>5.302</v>
       </c>
       <c r="G10">
-        <v>2.332</v>
+        <v>2.319</v>
       </c>
       <c r="H10">
-        <v>44.67</v>
+        <v>42.247</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -706,22 +706,22 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>2540</v>
+        <v>2555</v>
       </c>
       <c r="D11">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E11">
-        <v>3.416</v>
+        <v>3.397</v>
       </c>
       <c r="F11">
-        <v>4.944</v>
+        <v>4.929</v>
       </c>
       <c r="G11">
-        <v>-2.819</v>
+        <v>-2.802</v>
       </c>
       <c r="H11">
-        <v>46.916</v>
+        <v>44.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/prediksi/evaluasi_metode.xlsx
+++ b/output/prediksi/evaluasi_metode.xlsx
@@ -478,16 +478,16 @@
         <v>211</v>
       </c>
       <c r="E2">
-        <v>1.198</v>
+        <v>1.181</v>
       </c>
       <c r="F2">
-        <v>1.891</v>
+        <v>1.865</v>
       </c>
       <c r="G2">
-        <v>0.365</v>
+        <v>0.325</v>
       </c>
       <c r="H2">
-        <v>16.771</v>
+        <v>16.569</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -513,7 +513,7 @@
         <v>1.211</v>
       </c>
       <c r="H3">
-        <v>22.652</v>
+        <v>22.602</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -539,7 +539,7 @@
         <v>1.207</v>
       </c>
       <c r="H4">
-        <v>29.949</v>
+        <v>29.881</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -565,7 +565,7 @@
         <v>-1.477</v>
       </c>
       <c r="H5">
-        <v>33.093</v>
+        <v>33.027</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -591,7 +591,7 @@
         <v>-1.721</v>
       </c>
       <c r="H6">
-        <v>35.323</v>
+        <v>35.254</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -608,16 +608,16 @@
         <v>211</v>
       </c>
       <c r="E7">
-        <v>0.9340000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F7">
         <v>1.537</v>
       </c>
       <c r="G7">
-        <v>-0.11</v>
+        <v>-0.154</v>
       </c>
       <c r="H7">
-        <v>13.712</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -643,7 +643,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H8">
-        <v>16.354</v>
+        <v>16.316</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -669,7 +669,7 @@
         <v>0.645</v>
       </c>
       <c r="H9">
-        <v>16.719</v>
+        <v>16.687</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -695,7 +695,7 @@
         <v>2.319</v>
       </c>
       <c r="H10">
-        <v>42.247</v>
+        <v>42.178</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -721,7 +721,7 @@
         <v>-2.802</v>
       </c>
       <c r="H11">
-        <v>44.31</v>
+        <v>44.223</v>
       </c>
     </row>
   </sheetData>

--- a/output/prediksi/evaluasi_metode.xlsx
+++ b/output/prediksi/evaluasi_metode.xlsx
@@ -472,22 +472,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D2">
         <v>211</v>
       </c>
       <c r="E2">
-        <v>1.181</v>
+        <v>1.202</v>
       </c>
       <c r="F2">
-        <v>1.865</v>
+        <v>1.955</v>
       </c>
       <c r="G2">
-        <v>0.325</v>
+        <v>0.303</v>
       </c>
       <c r="H2">
-        <v>16.569</v>
+        <v>16.653</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -498,22 +498,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D3">
         <v>211</v>
       </c>
       <c r="E3">
-        <v>1.696</v>
+        <v>1.694</v>
       </c>
       <c r="F3">
         <v>2.701</v>
       </c>
       <c r="G3">
-        <v>1.211</v>
+        <v>1.219</v>
       </c>
       <c r="H3">
-        <v>22.602</v>
+        <v>22.592</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -524,22 +524,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D4">
         <v>211</v>
       </c>
       <c r="E4">
-        <v>2.271</v>
+        <v>2.261</v>
       </c>
       <c r="F4">
-        <v>3.827</v>
+        <v>3.821</v>
       </c>
       <c r="G4">
-        <v>1.207</v>
+        <v>1.187</v>
       </c>
       <c r="H4">
-        <v>29.881</v>
+        <v>29.781</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -550,7 +550,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D5">
         <v>211</v>
@@ -559,13 +559,13 @@
         <v>2.36</v>
       </c>
       <c r="F5">
-        <v>3.648</v>
+        <v>3.65</v>
       </c>
       <c r="G5">
-        <v>-1.477</v>
+        <v>-1.475</v>
       </c>
       <c r="H5">
-        <v>33.027</v>
+        <v>33.037</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -576,7 +576,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D6">
         <v>211</v>
@@ -585,13 +585,13 @@
         <v>2.53</v>
       </c>
       <c r="F6">
-        <v>3.86</v>
+        <v>3.862</v>
       </c>
       <c r="G6">
-        <v>-1.721</v>
+        <v>-1.72</v>
       </c>
       <c r="H6">
-        <v>35.254</v>
+        <v>35.272</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -602,22 +602,22 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D7">
         <v>211</v>
       </c>
       <c r="E7">
-        <v>0.9399999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="F7">
-        <v>1.537</v>
+        <v>1.501</v>
       </c>
       <c r="G7">
-        <v>-0.154</v>
+        <v>0.074</v>
       </c>
       <c r="H7">
-        <v>13.65</v>
+        <v>12.677</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -628,22 +628,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D8">
         <v>211</v>
       </c>
       <c r="E8">
-        <v>1.099</v>
+        <v>1.096</v>
       </c>
       <c r="F8">
-        <v>1.982</v>
+        <v>1.98</v>
       </c>
       <c r="G8">
-        <v>0.5600000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H8">
-        <v>16.316</v>
+        <v>16.299</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -654,22 +654,22 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D9">
         <v>211</v>
       </c>
       <c r="E9">
-        <v>1.168</v>
+        <v>1.169</v>
       </c>
       <c r="F9">
-        <v>2.166</v>
+        <v>2.167</v>
       </c>
       <c r="G9">
-        <v>0.645</v>
+        <v>0.647</v>
       </c>
       <c r="H9">
-        <v>16.687</v>
+        <v>16.698</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -680,22 +680,22 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D10">
         <v>211</v>
       </c>
       <c r="E10">
-        <v>3.134</v>
+        <v>3.129</v>
       </c>
       <c r="F10">
         <v>5.302</v>
       </c>
       <c r="G10">
-        <v>2.319</v>
+        <v>2.34</v>
       </c>
       <c r="H10">
-        <v>42.178</v>
+        <v>42.139</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -706,22 +706,22 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="D11">
         <v>211</v>
       </c>
       <c r="E11">
-        <v>3.397</v>
+        <v>3.402</v>
       </c>
       <c r="F11">
-        <v>4.929</v>
+        <v>4.934</v>
       </c>
       <c r="G11">
-        <v>-2.802</v>
+        <v>-2.807</v>
       </c>
       <c r="H11">
-        <v>44.223</v>
+        <v>44.294</v>
       </c>
     </row>
   </sheetData>
